--- a/conf1/chart-data.xlsx
+++ b/conf1/chart-data.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960"/>
+    <workbookView windowHeight="23960" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="chart-data" sheetId="1" r:id="rId1"/>
+    <sheet name="行为分析" sheetId="1" r:id="rId1"/>
+    <sheet name="实时分析" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t>应用ID</t>
   </si>
@@ -198,6 +199,30 @@
   </si>
   <si>
     <t>UGC</t>
+  </si>
+  <si>
+    <t>访问人数</t>
+  </si>
+  <si>
+    <t>访问次数</t>
+  </si>
+  <si>
+    <t>dailyVisitors</t>
+  </si>
+  <si>
+    <t>dailyVisits</t>
+  </si>
+  <si>
+    <t>dy_lite</t>
+  </si>
+  <si>
+    <t>抖音极速版</t>
+  </si>
+  <si>
+    <t>toutiao</t>
+  </si>
+  <si>
+    <t>今日头条</t>
   </si>
 </sst>
 </file>
@@ -820,11 +845,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1361,29 +1387,278 @@
   <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.2019230769231" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="1" customWidth="1"/>
-    <col min="13" max="13" width="27.7115384615385" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1923076923077" style="1" customWidth="1"/>
-    <col min="17" max="17" width="39.2692307692308" style="1" customWidth="1"/>
-    <col min="18" max="18" width="25" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23" style="1" customWidth="1"/>
-    <col min="20" max="20" width="22" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32" style="1" customWidth="1"/>
-    <col min="22" max="22" width="22.75" style="1" customWidth="1"/>
-    <col min="23" max="23" width="20" style="1" customWidth="1"/>
-    <col min="24" max="24" width="23" style="1" customWidth="1"/>
-    <col min="25" max="25" width="26" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="1"/>
+    <col min="1" max="6" width="12" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12" style="2" customWidth="1"/>
+    <col min="10" max="10" width="24.2019230769231" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.7115384615385" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.1923076923077" style="2" customWidth="1"/>
+    <col min="17" max="17" width="39.2692307692308" style="2" customWidth="1"/>
+    <col min="18" max="18" width="25" style="2" customWidth="1"/>
+    <col min="19" max="19" width="23" style="2" customWidth="1"/>
+    <col min="20" max="20" width="22" style="2" customWidth="1"/>
+    <col min="21" max="21" width="32" style="2" customWidth="1"/>
+    <col min="22" max="22" width="22.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="20" style="2" customWidth="1"/>
+    <col min="24" max="24" width="23" style="2" customWidth="1"/>
+    <col min="25" max="25" width="26" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:25">
+    <row r="1" s="2" customFormat="1" spans="1:25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:25">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:25">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>855</v>
+      </c>
+      <c r="G3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2">
+        <v>111</v>
+      </c>
+      <c r="I3" s="2">
+        <v>222</v>
+      </c>
+      <c r="J3" s="2">
+        <v>333</v>
+      </c>
+      <c r="K3" s="2">
+        <v>444</v>
+      </c>
+      <c r="L3" s="2">
+        <v>555</v>
+      </c>
+      <c r="M3" s="2">
+        <v>666</v>
+      </c>
+      <c r="N3" s="2">
+        <v>777</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" s="2">
+        <v>100</v>
+      </c>
+      <c r="S3" s="2">
+        <v>100</v>
+      </c>
+      <c r="T3" s="2">
+        <v>100</v>
+      </c>
+      <c r="U3" s="2">
+        <v>100</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" s="2">
+        <v>1286</v>
+      </c>
+      <c r="X3" s="2">
+        <v>5840</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>12.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1391,76 +1666,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:25">
+    <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1468,150 +1680,52 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:25">
+    <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="1">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1">
-        <v>855</v>
-      </c>
-      <c r="G3" s="1">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1">
-        <v>111</v>
-      </c>
-      <c r="I3" s="1">
-        <v>222</v>
-      </c>
-      <c r="J3" s="1">
-        <v>333</v>
-      </c>
-      <c r="K3" s="1">
-        <v>444</v>
-      </c>
-      <c r="L3" s="1">
-        <v>555</v>
-      </c>
-      <c r="M3" s="1">
-        <v>666</v>
-      </c>
-      <c r="N3" s="1">
-        <v>777</v>
-      </c>
-      <c r="O3" s="1">
-        <v>5000</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="1">
-        <v>100</v>
-      </c>
-      <c r="S3" s="1">
-        <v>100</v>
-      </c>
-      <c r="T3" s="1">
-        <v>100</v>
-      </c>
-      <c r="U3" s="1">
-        <v>100</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W3" s="1">
-        <v>1286</v>
-      </c>
-      <c r="X3" s="1">
-        <v>5840</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>12.35</v>
+      <c r="C3" s="1">
+        <v>68000</v>
+      </c>
+      <c r="D3" s="1">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1">
+        <v>32000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1">
+        <v>21000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>27500</v>
       </c>
     </row>
   </sheetData>

--- a/conf1/chart-data.xlsx
+++ b/conf1/chart-data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960" activeTab="1"/>
+    <workbookView windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="行为分析" sheetId="1" r:id="rId1"/>
@@ -75,22 +75,22 @@
     <t>总分享数</t>
   </si>
   <si>
-    <t>来源场景_场景ID</t>
-  </si>
-  <si>
-    <t>来源场景_场景名称</t>
-  </si>
-  <si>
-    <t>来源场景_日访问用户</t>
-  </si>
-  <si>
-    <t>来源场景_新增用户</t>
-  </si>
-  <si>
-    <t>来源场景_启动次数</t>
-  </si>
-  <si>
-    <t>来源场景_次均游戏时长</t>
+    <t>来源分析_场景ID</t>
+  </si>
+  <si>
+    <t>来源分析_场景名称</t>
+  </si>
+  <si>
+    <t>来源分析_日访问用户</t>
+  </si>
+  <si>
+    <t>来源分析_新增用户</t>
+  </si>
+  <si>
+    <t>来源分析_启动次数</t>
+  </si>
+  <si>
+    <t>来源分析_次均游戏时长</t>
   </si>
   <si>
     <t>视频数据_类型</t>

--- a/conf1/chart-data.xlsx
+++ b/conf1/chart-data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960"/>
+    <workbookView windowHeight="23260"/>
   </bookViews>
   <sheets>
     <sheet name="行为分析" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>应用ID</t>
   </si>
@@ -199,6 +199,15 @@
   </si>
   <si>
     <t>UGC</t>
+  </si>
+  <si>
+    <t>dy1</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>021037</t>
   </si>
   <si>
     <t>访问人数</t>
@@ -235,14 +244,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,141 +717,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1384,260 +1385,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:Y4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="6" width="12" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13" style="2" customWidth="1"/>
-    <col min="8" max="9" width="12" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24.2019230769231" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14" style="2" customWidth="1"/>
-    <col min="13" max="13" width="27.7115384615385" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13" style="2" customWidth="1"/>
-    <col min="16" max="16" width="20.1923076923077" style="2" customWidth="1"/>
-    <col min="17" max="17" width="39.2692307692308" style="2" customWidth="1"/>
-    <col min="18" max="18" width="25" style="2" customWidth="1"/>
-    <col min="19" max="19" width="23" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="2" customWidth="1"/>
-    <col min="21" max="21" width="32" style="2" customWidth="1"/>
-    <col min="22" max="22" width="22.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="20" style="2" customWidth="1"/>
-    <col min="24" max="24" width="23" style="2" customWidth="1"/>
-    <col min="25" max="25" width="26" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="1" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.2019230769231" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="27.7115384615385" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1923076923077" style="1" customWidth="1"/>
+    <col min="17" max="17" width="39.2692307692308" style="1" customWidth="1"/>
+    <col min="18" max="18" width="25" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23" style="1" customWidth="1"/>
+    <col min="20" max="20" width="22" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22.75" style="1" customWidth="1"/>
+    <col min="23" max="23" width="20" style="1" customWidth="1"/>
+    <col min="24" max="24" width="23" style="1" customWidth="1"/>
+    <col min="25" max="25" width="26" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:25">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:25">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:25">
+      <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:25">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:25">
+      <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>10</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>855</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>111</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>222</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>333</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>444</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>555</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>666</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>777</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>5000</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>100</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>100</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="1">
         <v>100</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U3" s="1">
         <v>100</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="1">
         <v>1286</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X3" s="1">
         <v>5840</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" s="1">
         <v>12.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="N4" s="1">
+        <v>888</v>
+      </c>
+      <c r="O4" s="1">
+        <v>999</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>22</v>
+      </c>
+      <c r="R4" s="1">
+        <v>101</v>
+      </c>
+      <c r="S4" s="1">
+        <v>101</v>
+      </c>
+      <c r="T4" s="1">
+        <v>101</v>
+      </c>
+      <c r="U4" s="1">
+        <v>101</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" s="1">
+        <v>1287</v>
+      </c>
+      <c r="X4" s="1">
+        <v>5841</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>13.35</v>
       </c>
     </row>
   </sheetData>
@@ -1666,10 +1715,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -1680,10 +1729,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -1702,10 +1751,10 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1">
         <v>32000</v>
@@ -1716,10 +1765,10 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1">
         <v>21000</v>

--- a/conf1/chart-data.xlsx
+++ b/conf1/chart-data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
   <si>
     <t>应用ID</t>
   </si>
@@ -201,7 +201,10 @@
     <t>UGC</t>
   </si>
   <si>
-    <t>dy1</t>
+    <t>dy_lite</t>
+  </si>
+  <si>
+    <t>抖音极速版</t>
   </si>
   <si>
     <t>2026-05-12</t>
@@ -220,12 +223,6 @@
   </si>
   <si>
     <t>dailyVisits</t>
-  </si>
-  <si>
-    <t>dy_lite</t>
-  </si>
-  <si>
-    <t>抖音极速版</t>
   </si>
   <si>
     <t>toutiao</t>
@@ -1388,7 +1385,9 @@
   <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="6" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1057692307692" style="1" customWidth="1"/>
+    <col min="3" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" customWidth="1"/>
     <col min="8" max="9" width="12" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.2019230769231" style="1" customWidth="1"/>
@@ -1646,10 +1645,10 @@
         <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="1"/>
       <c r="N4" s="1">
@@ -1659,7 +1658,7 @@
         <v>999</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="1">
         <v>22</v>
@@ -1715,10 +1714,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -1729,10 +1728,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -1751,10 +1750,10 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1">
         <v>32000</v>
@@ -1765,10 +1764,10 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C5" s="1">
         <v>21000</v>
